--- a/artfynd/A 19918-2022 artfynd.xlsx
+++ b/artfynd/A 19918-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125894614</v>
       </c>
       <c r="B2" t="n">
-        <v>58153</v>
+        <v>58154</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125894613</v>
       </c>
       <c r="B3" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19918-2022 artfynd.xlsx
+++ b/artfynd/A 19918-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125894614</v>
       </c>
       <c r="B2" t="n">
-        <v>58154</v>
+        <v>58155</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125894613</v>
       </c>
       <c r="B3" t="n">
-        <v>57980</v>
+        <v>57981</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19918-2022 artfynd.xlsx
+++ b/artfynd/A 19918-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125894614</v>
       </c>
       <c r="B2" t="n">
-        <v>58155</v>
+        <v>58159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125894613</v>
       </c>
       <c r="B3" t="n">
-        <v>57981</v>
+        <v>57985</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 19918-2022 artfynd.xlsx
+++ b/artfynd/A 19918-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125894614</v>
       </c>
       <c r="B2" t="n">
-        <v>58159</v>
+        <v>58162</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>125894613</v>
       </c>
       <c r="B3" t="n">
-        <v>57985</v>
+        <v>57987</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
